--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484080_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484080_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0305</v>
+        <v>3.2113</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3764</v>
+        <v>1.5011</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6541</v>
+        <v>1.7103</v>
       </c>
       <c r="G2" t="n">
         <v>2.4542</v>
@@ -610,13 +610,13 @@
         <v>2.7774</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9432</v>
+        <v>-0.7624</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1926</v>
+        <v>-0.0679</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.6944</v>
       </c>
       <c r="V2" t="n">
         <v>-0.266</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CRUZ JOBACHO</t>
+          <t>I. VILLAR CANTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6625</v>
+        <v>2.9196</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4288</v>
+        <v>3.2376</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0913</v>
+        <v>-0.3181</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9179</v>
+        <v>2.2248</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3557</v>
+        <v>1.4773</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4378</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3986</v>
+        <v>2.8497</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9985000000000001</v>
+        <v>2.4003</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5999</v>
+        <v>0.4494</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5192</v>
+        <v>-0.6249</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3572</v>
+        <v>-0.923</v>
       </c>
       <c r="O3" t="n">
-        <v>0.162</v>
+        <v>0.2981</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6733</v>
+        <v>-0.3684</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1564</v>
+        <v>0.7766</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4831</v>
+        <v>-1.1451</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6745</v>
+        <v>0.0713</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6745</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3379</v>
+        <v>2.7624</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4672</v>
+        <v>1.8356</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8707</v>
+        <v>0.9268</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9586</v>
@@ -766,13 +766,13 @@
         <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5214</v>
+        <v>-1.0968</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2267</v>
+        <v>0.1417</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2947</v>
+        <v>-1.2386</v>
       </c>
       <c r="V4" t="n">
         <v>4.2226</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. OLAGUIBE GONZALEZ</t>
+          <t>A. CRUZ JOBACHO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2627</v>
+        <v>2.23</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1113</v>
+        <v>-0.4685</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1514</v>
+        <v>2.6985</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6348</v>
+        <v>0.9179</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0505</v>
+        <v>1.3557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5843</v>
+        <v>-0.4378</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3383</v>
+        <v>0.3986</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9784</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.64</v>
+        <v>-0.5999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2965</v>
+        <v>0.5192</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9278</v>
+        <v>0.3572</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2244</v>
+        <v>0.162</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5871</v>
+        <v>2.3806</v>
       </c>
       <c r="S5" t="n">
-        <v>1.37</v>
+        <v>0.2409</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2924</v>
+        <v>1.1167</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0775</v>
+        <v>-0.8759</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3373</v>
+        <v>0.6745</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8097</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. VILLAR CANTERO</t>
+          <t>E. NOGUES MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9481</v>
+        <v>1.3735</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6028</v>
+        <v>0.4761</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6546999999999999</v>
+        <v>0.8974</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2248</v>
+        <v>1.4034</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4773</v>
+        <v>-0.8561</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7475000000000001</v>
+        <v>2.2595</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8497</v>
+        <v>2.0857</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4003</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4494</v>
+        <v>1.2877</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6249</v>
+        <v>-0.6823</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.923</v>
+        <v>-1.6541</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2981</v>
+        <v>0.9718</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9919</v>
+        <v>2.9758</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>3.9677</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3399</v>
+        <v>-0.5215</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1418</v>
+        <v>0.7313</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.4817</v>
+        <v>-1.2528</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0713</v>
+        <v>-2.4842</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6032</v>
+        <v>-1.349</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.532</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIEZ VALERO</t>
+          <t>H. OLAGUIBE GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4367</v>
+        <v>1.2002</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9434</v>
+        <v>1.3574</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3801</v>
+        <v>-0.1572</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6932</v>
+        <v>0.6348</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3579</v>
+        <v>0.0505</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6646</v>
+        <v>0.5843</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.2699</v>
+        <v>0.3383</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.7102</v>
+        <v>0.9784</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5597</v>
+        <v>-0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5767</v>
+        <v>0.2965</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3523</v>
+        <v>-0.9278</v>
       </c>
       <c r="O7" t="n">
         <v>1.2244</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9758</v>
+        <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>1.412</v>
+        <v>0.3075</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3184</v>
+        <v>0.5386</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9064</v>
+        <v>-0.2311</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.266</v>
+        <v>-0.3373</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.266</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6432</v>
+        <v>0.9822</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.986</v>
+        <v>-1.7593</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6292</v>
+        <v>2.7414</v>
       </c>
       <c r="G8" t="n">
         <v>0.5348000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>2.9758</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8321</v>
+        <v>-0.4931</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1189</v>
+        <v>0.1078</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7131</v>
+        <v>-0.6009</v>
       </c>
       <c r="V8" t="n">
         <v>0.9405</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4206</v>
+        <v>0.3489</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6219</v>
+        <v>-0.4972</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0425</v>
+        <v>0.8461</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2671</v>
@@ -1156,13 +1156,13 @@
         <v>2.7774</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7091</v>
+        <v>-0.7808</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2665</v>
+        <v>0.3912</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9756</v>
+        <v>-1.172</v>
       </c>
       <c r="V9" t="n">
         <v>0.6032</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. NOGUES MARTIN</t>
+          <t>A. DIEZ VALERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.258</v>
+        <v>0.267</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5272</v>
+        <v>-3.3095</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7852</v>
+        <v>3.5764</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4034</v>
+        <v>-1.6932</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8561</v>
+        <v>-2.3579</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2595</v>
+        <v>0.6646</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0857</v>
+        <v>-3.2699</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7979000000000001</v>
+        <v>-2.7102</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2877</v>
+        <v>-0.5597</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6823</v>
+        <v>1.5767</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6541</v>
+        <v>0.3523</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9718</v>
+        <v>1.2244</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9758</v>
+        <v>1.9838</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>3.9677</v>
+        <v>2.9758</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6369</v>
+        <v>0.2423</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2719</v>
+        <v>0.9523</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.365</v>
+        <v>-0.71</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4842</v>
+        <v>-0.266</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.349</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1352</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="11">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6045</v>
+        <v>-2.9643</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0646</v>
+        <v>-3.4524</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4601</v>
+        <v>0.4881</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2794</v>
@@ -1390,13 +1390,13 @@
         <v>1.3887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7975</v>
+        <v>-0.1573</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1757</v>
+        <v>0.4365</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6218</v>
+        <v>-0.5938</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9405</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.2022</v>
+        <v>12.1373</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.065200000000001</v>
+        <v>-1.130100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>13.2674</v>
+        <v>13.2672</v>
       </c>
       <c r="G13" t="n">
         <v>4.704400000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.1056</v>
+        <v>-4.105600000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>8.809900000000001</v>
+        <v>8.809899999999999</v>
       </c>
       <c r="J13" t="n">
         <v>2.6418</v>
@@ -1453,13 +1453,13 @@
         <v>2.0625</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.549599999999999</v>
+        <v>-5.5496</v>
       </c>
       <c r="O13" t="n">
         <v>7.612200000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>8.9274</v>
+        <v>8.927400000000002</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.8706</v>
@@ -1468,22 +1468,22 @@
         <v>24.7982</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.647900000000001</v>
+        <v>-3.7127</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1387</v>
+        <v>5.073799999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-8.7865</v>
+        <v>-8.786700000000002</v>
       </c>
       <c r="V13" t="n">
-        <v>2.218099999999999</v>
+        <v>2.2181</v>
       </c>
       <c r="W13" t="n">
-        <v>7.024900000000001</v>
+        <v>7.0249</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.806800000000001</v>
+        <v>-4.8068</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1015</v>
+        <v>3.2114</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6123</v>
+        <v>2.0616</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4891</v>
+        <v>1.1498</v>
       </c>
       <c r="G14" t="n">
         <v>2.8973</v>
@@ -1546,13 +1546,13 @@
         <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9264</v>
+        <v>2.0363</v>
       </c>
       <c r="T14" t="n">
-        <v>4.6594</v>
+        <v>2.1086</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7329</v>
+        <v>-0.0723</v>
       </c>
       <c r="V14" t="n">
         <v>-0.532</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0298</v>
+        <v>0.8616</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5709</v>
+        <v>1.3465</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.541</v>
+        <v>-0.4849</v>
       </c>
       <c r="G15" t="n">
         <v>1.4029</v>
@@ -1624,13 +1624,13 @@
         <v>0.9919</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6189</v>
+        <v>0.4506</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9103</v>
+        <v>0.6859</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2914</v>
+        <v>-0.2353</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>R. SOLIVELLES MENDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4962</v>
+        <v>0.5615</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2267</v>
+        <v>-0.9615</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7228</v>
+        <v>1.523</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4786</v>
+        <v>-1.1517</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3425</v>
+        <v>0.4431</v>
       </c>
       <c r="I16" t="n">
-        <v>0.136</v>
+        <v>-1.5949</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-1.4661</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.4138</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.8799</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4786</v>
+        <v>0.3144</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3425</v>
+        <v>0.0293</v>
       </c>
       <c r="O16" t="n">
-        <v>0.136</v>
+        <v>0.2851</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6127</v>
+        <v>0.999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7652</v>
+        <v>1.1791</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1525</v>
+        <v>-0.1801</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. SOLIVELLES MENDEZ</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1797</v>
+        <v>0.1399</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2676</v>
+        <v>-0.6348</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4473</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1517</v>
+        <v>0.4786</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4431</v>
+        <v>0.3425</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5949</v>
+        <v>0.136</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4661</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4138</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.8799</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3144</v>
+        <v>0.4786</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0293</v>
+        <v>0.3425</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2851</v>
+        <v>0.136</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3887</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6172</v>
+        <v>0.2565</v>
       </c>
       <c r="T17" t="n">
-        <v>0.873</v>
+        <v>0.3571</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2558</v>
+        <v>-0.1006</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. NEALE GIMENEZ-CASSINA</t>
+          <t>W. MCDONALD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4641</v>
+        <v>-0.0648</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1133</v>
+        <v>-1.6615</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3507</v>
+        <v>1.5967</v>
       </c>
       <c r="G18" t="n">
-        <v>0.077</v>
+        <v>1.133</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3425</v>
+        <v>1.6877</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2656</v>
+        <v>-0.5546</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.3911</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>0.077</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3425</v>
+        <v>0.2965</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2656</v>
+        <v>0.2786</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5952</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.267</v>
+        <v>-0.333</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1133</v>
+        <v>-0.1643</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1536</v>
+        <v>-0.1687</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8692</v>
+        <v>-0.0713</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.0713</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W. MCDONALD</t>
+          <t>A. NEALE GIMENEZ-CASSINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6268</v>
+        <v>-0.1418</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1716</v>
+        <v>-0.0113</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5448</v>
+        <v>-0.1305</v>
       </c>
       <c r="G19" t="n">
-        <v>1.133</v>
+        <v>0.077</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6877</v>
+        <v>0.3425</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5546</v>
+        <v>-0.2656</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5580000000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3911</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2965</v>
+        <v>0.3425</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2786</v>
+        <v>-0.2656</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.895</v>
+        <v>0.0553</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6744</v>
+        <v>-0.0113</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2206</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0713</v>
+        <v>-0.8692</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0713</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7976</v>
+        <v>-0.9686</v>
       </c>
       <c r="E20" t="n">
         <v>-2.139</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3415</v>
+        <v>1.1704</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7656</v>
@@ -2014,13 +2014,13 @@
         <v>1.9838</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1503</v>
+        <v>0.9792</v>
       </c>
       <c r="T20" t="n">
         <v>1.0317</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8815</v>
+        <v>-0.0525</v>
       </c>
       <c r="V20" t="n">
         <v>1.8097</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. GANDOL COBO</t>
+          <t>D. IRUELA RUBIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7064</v>
+        <v>-1.9206</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0364</v>
+        <v>-2.1124</v>
       </c>
       <c r="F21" t="n">
-        <v>0.33</v>
+        <v>0.1919</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7084</v>
+        <v>-1.0693</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7486</v>
+        <v>1.8237</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0402</v>
+        <v>-2.893</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.6</v>
+        <v>-0.6445</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.9599</v>
+        <v>1.996</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.64</v>
+        <v>-2.6405</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8915999999999999</v>
+        <v>-0.4249</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2114</v>
+        <v>-0.1723</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6802</v>
+        <v>-0.2526</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0612</v>
+        <v>0.1488</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5555</v>
+        <v>0.5159</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6167</v>
+        <v>-0.3671</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1352</v>
+        <v>-0.6032</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1352</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>E. GANDOL COBO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1672</v>
+        <v>-2.1181</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.54</v>
+        <v>-2.8323</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6272</v>
+        <v>0.7143</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6692</v>
+        <v>-1.7084</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6229</v>
+        <v>-1.7486</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9537</v>
+        <v>0.0402</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1548</v>
+        <v>-2.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4607</v>
+        <v>-1.9599</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.306</v>
+        <v>-0.64</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4855</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8378</v>
+        <v>0.2114</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.6802</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.1741</v>
+        <v>0.1984</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.9515</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7774</v>
+        <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6155</v>
+        <v>0.5271</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0849</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7004</v>
+        <v>-0.2324</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2777</v>
+        <v>-1.1352</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3417</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.6194</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. IRUELA RUBIO</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2512</v>
+        <v>-2.4563</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0307</v>
+        <v>-0.3156</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2205</v>
+        <v>-2.1407</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0693</v>
+        <v>0.6692</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8237</v>
+        <v>1.6229</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.893</v>
+        <v>-0.9537</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6445</v>
+        <v>2.1548</v>
       </c>
       <c r="K23" t="n">
-        <v>1.996</v>
+        <v>2.4607</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6405</v>
+        <v>-0.306</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4249</v>
+        <v>-1.4855</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1723</v>
+        <v>-0.8378</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2526</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3968</v>
+        <v>-3.1741</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9838</v>
+        <v>-5.9515</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5871</v>
+        <v>2.7774</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1818</v>
+        <v>1.3263</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4024</v>
+        <v>1.1395</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7795</v>
+        <v>0.1869</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6032</v>
+        <v>-1.2777</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.3417</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6032</v>
+        <v>-3.6194</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.996</v>
+        <v>-5.5855</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.9251</v>
+        <v>-6.0069</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0709</v>
+        <v>0.4214</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6674</v>
@@ -2326,13 +2326,13 @@
         <v>1.9838</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.488</v>
+        <v>0.9225</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2665</v>
+        <v>1.1847</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.2622</v>
       </c>
       <c r="V24" t="n">
         <v>1.1352</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.2021</v>
+        <v>-8.481300000000001</v>
       </c>
       <c r="E25" t="n">
         <v>-13.2672</v>
       </c>
       <c r="F25" t="n">
-        <v>2.065199999999999</v>
+        <v>4.7861</v>
       </c>
       <c r="G25" t="n">
         <v>-4.7044</v>
@@ -2374,7 +2374,7 @@
         <v>4.1055</v>
       </c>
       <c r="I25" t="n">
-        <v>-8.810099999999998</v>
+        <v>-8.8101</v>
       </c>
       <c r="J25" t="n">
         <v>-2.0626</v>
@@ -2404,13 +2404,13 @@
         <v>15.8708</v>
       </c>
       <c r="S25" t="n">
-        <v>4.648</v>
+        <v>7.368600000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>8.786600000000002</v>
+        <v>8.7865</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.138599999999999</v>
+        <v>-1.4177</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2182</v>
